--- a/docs/missing-sticker-art.xlsx
+++ b/docs/missing-sticker-art.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing art'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing art'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -509,19 +509,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Franz Beckenbauer</t>
+          <t>Kylian Mbappé</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1974</v>
+        <v>2026</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>97</v>
@@ -538,29 +538,29 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ger-1974-5.webp</t>
+          <t>fra-2026-10.webp</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kylian Mbappé</t>
+          <t>Johan Cruyff</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2026</v>
+        <v>1974</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -574,29 +574,29 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>fra-2026-10.webp</t>
+          <t>ned-1974-14.webp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Johan Cruyff</t>
+          <t>Erling Haaland</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1974</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -610,26 +610,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ned-1974-14.webp</t>
+          <t>nor-2026-9.webp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paolo Rossi</t>
+          <t>Lionel Messi</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1982</v>
+        <v>2026</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>94</v>
@@ -646,29 +646,29 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ita-1982-20.webp</t>
+          <t>arg-2026-10.webp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Erling Haaland</t>
+          <t>Gerd Müller</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2026</v>
+        <v>1970</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -682,29 +682,29 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>nor-2026-9.webp</t>
+          <t>ger-1970-13.webp</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lionel Messi</t>
+          <t>Rodri</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>2026</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -718,26 +718,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>arg-2026-10.webp</t>
+          <t>esp-2026-16.webp</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gerd Müller</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1970</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>93</v>
@@ -754,33 +754,33 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ger-1970-13.webp</t>
+          <t>esp-2026-19.webp</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rodri</t>
+          <t>Gérson</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2026</v>
+        <v>1970</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Iconic</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -790,33 +790,33 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>esp-2026-16.webp</t>
+          <t>bra-1970-8.webp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Franz Beckenbauer</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2026</v>
+        <v>1970</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iconic</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -826,26 +826,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>esp-2026-19.webp</t>
+          <t>ger-1970-4.webp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gérson</t>
+          <t>Alain Giresse</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1970</v>
+        <v>1982</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>92</v>
@@ -862,26 +862,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>bra-1970-8.webp</t>
+          <t>fra-1982-12.webp</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Franz Beckenbauer</t>
+          <t>Vinícius Júnior</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1970</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>92</v>
@@ -898,26 +898,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ger-1970-4.webp</t>
+          <t>bra-2026-7.webp</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alain Giresse</t>
+          <t>Jude Bellingham</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1982</v>
+        <v>2026</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>92</v>
@@ -934,29 +934,29 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>fra-1982-12.webp</t>
+          <t>eng-2026-10.webp</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vinícius Júnior</t>
+          <t>Michel Platini</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2026</v>
+        <v>1982</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -970,29 +970,29 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>bra-2026-7.webp</t>
+          <t>fra-1982-10.webp</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jude Bellingham</t>
+          <t>Rivellino</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2026</v>
+        <v>1970</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1006,29 +1006,29 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>eng-2026-10.webp</t>
+          <t>bra-1970-11.webp</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gerd Müller</t>
+          <t>Bobby Moore</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1974</v>
+        <v>1970</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1042,29 +1042,29 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ger-1974-13.webp</t>
+          <t>eng-1970-6.webp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mario Kempes</t>
+          <t>Johan Neeskens</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1078,29 +1078,29 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>arg-1978-10.webp</t>
+          <t>ned-1974-13.webp</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Michel Platini</t>
+          <t>Kazimierz Deyna</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1982</v>
+        <v>1974</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1114,26 +1114,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>fra-1982-10.webp</t>
+          <t>pol-1974-12.webp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rivellino</t>
+          <t>Rob Rensenbrink</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>90</v>
@@ -1150,26 +1150,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>bra-1970-11.webp</t>
+          <t>ned-1978-12.webp</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bobby Moore</t>
+          <t>Karl-Heinz Rummenigge</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1970</v>
+        <v>1982</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>90</v>
@@ -1186,26 +1186,26 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>eng-1970-6.webp</t>
+          <t>ger-1982-11.webp</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Johan Neeskens</t>
+          <t>Zbigniew Boniek</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1974</v>
+        <v>1982</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>90</v>
@@ -1222,26 +1222,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ned-1974-13.webp</t>
+          <t>pol-1982-20.webp</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kazimierz Deyna</t>
+          <t>Zico</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1974</v>
+        <v>1982</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>90</v>
@@ -1258,26 +1258,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>pol-1974-12.webp</t>
+          <t>bra-1982-10.webp</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rob Rensenbrink</t>
+          <t>Michel Platini</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1978</v>
+        <v>1986</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>90</v>
@@ -1294,26 +1294,26 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ned-1978-12.webp</t>
+          <t>fra-1986-10.webp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Karl-Heinz Rummenigge</t>
+          <t>Emilio Butragueño</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>90</v>
@@ -1330,26 +1330,26 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ger-1982-11.webp</t>
+          <t>esp-1986-9.webp</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Zbigniew Boniek</t>
+          <t>Gary Lineker</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>90</v>
@@ -1366,14 +1366,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>pol-1982-20.webp</t>
+          <t>eng-1986-10.webp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zico</t>
+          <t>Preben Elkjær</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -1381,11 +1381,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>90</v>
@@ -1402,22 +1402,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>bra-1982-10.webp</t>
+          <t>den-1986-10.webp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Michel Platini</t>
+          <t>Ihor Belanov</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Soviet Union</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1438,26 +1438,26 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>fra-1986-10.webp</t>
+          <t>urs-1986-19.webp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Emilio Butragueño</t>
+          <t>Achraf Hakimi</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1986</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>90</v>
@@ -1474,26 +1474,26 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>esp-1986-9.webp</t>
+          <t>mar-2026-2.webp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gary Lineker</t>
+          <t>Thibaut Courtois</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1986</v>
+        <v>2026</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>90</v>
@@ -1510,26 +1510,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>eng-1986-10.webp</t>
+          <t>bel-2026-1.webp</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Preben Elkjær</t>
+          <t>Ousmane Dembélé</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1986</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>90</v>
@@ -1546,156 +1546,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>den-1986-10.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Ihor Belanov</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Soviet Union</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>1986</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>urs-1986-19.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Achraf Hakimi</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>mar-2026-2.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Thibaut Courtois</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>bel-2026-1.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Ousmane Dembélé</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
           <t>fra-2026-7.webp</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:H30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1744,7 +1600,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a5675bb</t>
+          <t>7756263</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1612,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6c2eaf7428b133be</t>
+          <t>d1a704cc5f51f412</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1644,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTA('Missing art'!$A$2:$A$34)</f>
+        <f>COUNTA('Missing art'!$A$2:$A$30)</f>
         <v/>
       </c>
     </row>
@@ -1799,7 +1655,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Missing art'!$G$2:$G$34,"yes")</f>
+        <f>COUNTIF('Missing art'!$G$2:$G$30,"yes")</f>
         <v/>
       </c>
     </row>
@@ -1817,7 +1673,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>COUNTIF('Missing art'!$F$2:$F$34,A12)</f>
+        <f>COUNTIF('Missing art'!$F$2:$F$30,A12)</f>
         <v/>
       </c>
     </row>
@@ -1828,7 +1684,7 @@
         </is>
       </c>
       <c r="B13">
-        <f>COUNTIF('Missing art'!$F$2:$F$34,A13)</f>
+        <f>COUNTIF('Missing art'!$F$2:$F$30,A13)</f>
         <v/>
       </c>
     </row>
@@ -1839,7 +1695,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF('Missing art'!$F$2:$F$34,A14)</f>
+        <f>COUNTIF('Missing art'!$F$2:$F$30,A14)</f>
         <v/>
       </c>
     </row>
@@ -1891,7 +1747,7 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>A card is one player at one tournament, so the same man needs a card for each. On this list: Franz Beckenbauer (1970 and 1974), Gerd Müller (1970 and 1974), Michel Platini (1982 and 1986).</t>
+          <t>A card is one player at one tournament, so the same man needs a card for each. On this list: Michel Platini (1982 and 1986).</t>
         </is>
       </c>
     </row>

--- a/docs/missing-sticker-art.xlsx
+++ b/docs/missing-sticker-art.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing art'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Missing art'!$A$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -75,9 +75,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -451,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -460,8 +457,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,12 +491,7 @@
           <t>Tier</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>File to add</t>
         </is>
@@ -524,19 +515,14 @@
         <v>2026</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monumental</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+          <t>Iconic</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>fra-2026-10.webp</t>
         </is>
@@ -567,12 +553,7 @@
           <t>Iconic</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>ned-1974-14.webp</t>
         </is>
@@ -603,12 +584,7 @@
           <t>Iconic</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>nor-2026-9.webp</t>
         </is>
@@ -639,12 +615,7 @@
           <t>Iconic</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>arg-2026-10.webp</t>
         </is>
@@ -675,12 +646,7 @@
           <t>Iconic</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ger-1970-13.webp</t>
         </is>
@@ -711,12 +677,7 @@
           <t>Iconic</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>esp-2026-16.webp</t>
         </is>
@@ -747,12 +708,7 @@
           <t>Iconic</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>esp-2026-19.webp</t>
         </is>
@@ -783,12 +739,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>bra-1970-8.webp</t>
         </is>
@@ -819,12 +770,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>ger-1970-4.webp</t>
         </is>
@@ -855,12 +801,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>fra-1982-12.webp</t>
         </is>
@@ -891,12 +832,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>bra-2026-7.webp</t>
         </is>
@@ -927,12 +863,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>eng-2026-10.webp</t>
         </is>
@@ -963,12 +894,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>fra-1982-10.webp</t>
         </is>
@@ -999,12 +925,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>bra-1970-11.webp</t>
         </is>
@@ -1035,12 +956,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>eng-1970-6.webp</t>
         </is>
@@ -1071,12 +987,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>ned-1974-13.webp</t>
         </is>
@@ -1107,12 +1018,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>pol-1974-12.webp</t>
         </is>
@@ -1143,12 +1049,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>ned-1978-12.webp</t>
         </is>
@@ -1179,12 +1080,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>ger-1982-11.webp</t>
         </is>
@@ -1215,12 +1111,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>pol-1982-20.webp</t>
         </is>
@@ -1251,12 +1142,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>bra-1982-10.webp</t>
         </is>
@@ -1287,12 +1173,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>fra-1986-10.webp</t>
         </is>
@@ -1323,12 +1204,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>esp-1986-9.webp</t>
         </is>
@@ -1359,12 +1235,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>eng-1986-10.webp</t>
         </is>
@@ -1395,12 +1266,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>den-1986-10.webp</t>
         </is>
@@ -1431,12 +1297,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>urs-1986-19.webp</t>
         </is>
@@ -1467,12 +1328,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>mar-2026-2.webp</t>
         </is>
@@ -1503,12 +1359,7 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>bel-2026-1.webp</t>
         </is>
@@ -1539,19 +1390,14 @@
           <t>Legendary</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>fra-2026-7.webp</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:G30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1574,14 +1420,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Sticker art still to draw</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Card set last changed</t>
         </is>
@@ -1593,31 +1439,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>with the dataset at commit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7756263</t>
+          <t>0121695</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Fingerprint</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>d1a704cc5f51f412</t>
+          <t>80a59723c9bb44b5</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Collectibles in the dataset</t>
         </is>
@@ -1627,7 +1473,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>With artwork</t>
         </is>
@@ -1638,7 +1484,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Missing (rows on the list)</t>
         </is>
@@ -1648,19 +1494,8 @@
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Of those, accepted as silhouettes</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>COUNTIF('Missing art'!$G$2:$G$30,"yes")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Missing by tier</t>
         </is>
@@ -1711,14 +1546,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Generated by `npm run ratings:sync`. Do not edit by hand: the next rating change rewrites this file, and every figure above is derived from the dataset at the commit named in B4.</t>
         </is>
@@ -1727,25 +1562,25 @@
     <row r="19"/>
     <row r="20"/>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>To draw a card: save the full-size PNG as art/stickers-src/&lt;id&gt;.png, where &lt;id&gt; is the file name in the last column minus .webp, then run `npm run ratings:sync`. It builds the small WebP the site serves and takes the card off the waiting list.</t>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>To draw a card: save the full-size PNG as art/stickers-src/&lt;id&gt;.png, where &lt;id&gt; is the file name in the last column minus .webp, then run `npm run ratings:sync`. It builds the small WebP the site serves and takes the card off the list.</t>
         </is>
       </c>
     </row>
     <row r="23"/>
     <row r="24"/>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>A row saying NO in Accepted is failing the build right now: either draw it or accept it as a silhouette with `npm run ratings:sync -- --accept-all`.</t>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Nothing here is broken or failing. A card with no artwork shows a silhouette at the same size in the album, so this is a worklist rather than a fault list. The command above names the cards that appeared since the last time it ran, which is how a rating change that creates a new collectible gets noticed.</t>
         </is>
       </c>
     </row>
     <row r="27"/>
     <row r="28"/>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>A card is one player at one tournament, so the same man needs a card for each. On this list: Michel Platini (1982 and 1986).</t>
         </is>
